--- a/evaluations/results/EXECUTIVE_PERFORMANCE_REPORT_V7_final.xlsx
+++ b/evaluations/results/EXECUTIVE_PERFORMANCE_REPORT_V7_final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/himanth/PCB/main_ST_AI/Main/AI-Enabled-Ticketing-System-main 6/evaluations/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE9B616-E772-7D4F-BE0D-B59D00D8F0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2215F985-254C-1A47-BD6E-AE391F10A676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1_FULL_BENCHMARK_DATA" sheetId="1" r:id="rId1"/>
@@ -1174,9 +1174,6 @@
     <t>0.90</t>
   </si>
   <si>
-    <t>Best semantic alignment with the "Golden Answer" meaning.</t>
-  </si>
-  <si>
     <t>Operational Speed</t>
   </si>
   <si>
@@ -1187,6 +1184,9 @@
   </si>
   <si>
     <t>Context</t>
+  </si>
+  <si>
+    <t>Best semantic alignment with the "Knowledge Base Answer" meaning.</t>
   </si>
 </sst>
 </file>
@@ -1601,7 +1601,7 @@
     <col min="13" max="13" width="20" customWidth="1"/>
     <col min="14" max="14" width="21" customWidth="1"/>
     <col min="15" max="15" width="24" customWidth="1"/>
-    <col min="16" max="16" width="26" customWidth="1"/>
+    <col min="16" max="16" width="24.6640625" customWidth="1"/>
     <col min="17" max="17" width="18" customWidth="1"/>
     <col min="18" max="18" width="24" customWidth="1"/>
     <col min="19" max="19" width="22" customWidth="1"/>
@@ -8065,7 +8065,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B2" t="s">
         <v>180</v>
@@ -8359,21 +8359,21 @@
         <v>246</v>
       </c>
       <c r="D6" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B7" t="s">
         <v>242</v>
       </c>
       <c r="C7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D7" t="s">
         <v>249</v>
-      </c>
-      <c r="D7" t="s">
-        <v>250</v>
       </c>
     </row>
   </sheetData>
